--- a/docs/oc-top-organismos/endoprotesis-ortopedia-y-trauma.xlsx
+++ b/docs/oc-top-organismos/endoprotesis-ortopedia-y-trauma.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M150"/>
+  <dimension ref="A1:M197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>20353.92</v>
+        <v>20417.96</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>6331.55</v>
+        <v>6293.61</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>5170.24</v>
+        <v>5228.06</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>5727.51</v>
+        <v>5770.89</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>7276.48</v>
+        <v>7304.05</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>33708.48</v>
+        <v>33623.37</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>15161.52</v>
+        <v>15123.24</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>6778.31</v>
+        <v>6761.2</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>56594.6</v>
+        <v>56451.71</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>28423.04</v>
+        <v>28351.28</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>5053.04</v>
+        <v>5040.29</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>36896.08</v>
+        <v>37246.62</v>
       </c>
     </row>
     <row r="14">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>5209.15</v>
+        <v>5247.96</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3378-4411-CM26</t>
+          <t>1057049-15034-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,22 +1322,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>6363.37</v>
+        <v>77145.61</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2069-4280-CM26</t>
+          <t>2069-4170-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>3606.63</v>
+        <v>3597.72</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2069-4234-CM26</t>
+          <t>2069-4231-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>3606.63</v>
+        <v>3597.72</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2069-4326-CM26</t>
+          <t>2069-4233-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>7213.25</v>
+        <v>3597.72</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2069-4231-CM26</t>
+          <t>2069-4234-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>3606.63</v>
+        <v>3597.72</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2069-4170-CM26</t>
+          <t>2069-4280-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>3606.63</v>
+        <v>3597.72</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2069-4233-CM26</t>
+          <t>2069-4326-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>3606.63</v>
+        <v>7195.44</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>3606.63</v>
+        <v>3624.34</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3635.44</v>
+        <v>3653.3</v>
       </c>
     </row>
     <row r="24">
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>75767.67999999999</v>
+        <v>76139.87</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>812030-528-CM26</t>
+          <t>1549-2292-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>HOSPITALIA Productos Medicos Ltda</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>4319.14</v>
+        <v>24082.25</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1549-2292-CM26</t>
+          <t>812030-528-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>24002.62</v>
+        <v>4333.46</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1057539-3987-CM26</t>
+          <t>812030-608-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2059,32 +2059,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2770.05</v>
+        <v>46999.57</v>
       </c>
     </row>
     <row r="28">
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>36227.15</v>
+        <v>36342.45</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>812030-608-CM26</t>
+          <t>1057539-3987-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2181,32 +2181,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>HOSPITALIA Productos Medicos Ltda</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>46850.45</v>
+        <v>2778.87</v>
       </c>
     </row>
     <row r="30">
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>7242.12</v>
+        <v>7280.63</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3378-4541-CM26</t>
+          <t>608-6675-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2308,27 +2308,27 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>2673.58</v>
+        <v>4256.71</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>608-6675-CM26</t>
+          <t>812030-622-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2359,37 +2359,37 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>4207.36</v>
+        <v>3006.57</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>812030-622-CM26</t>
+          <t>812030-650-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>2976.3</v>
+        <v>6388.66</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3378-4788-CM26</t>
+          <t>1057539-4333-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2481,37 +2481,37 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>63228.9</v>
+        <v>4450.7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>812030-650-CM26</t>
+          <t>812030-659-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>6437.49</v>
+        <v>4232.69</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1057539-4333-CM26</t>
+          <t>1952-1368-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2613,17 +2613,17 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.602.248-2</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>Hospital Villarrica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>4514.77</v>
+        <v>3590.8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>812030-659-CM26</t>
+          <t>812030-669-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>4291.66</v>
+        <v>5602.96</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>812030-669-CM26</t>
+          <t>1952-1225-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2735,27 +2735,27 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.602.248-2</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>Hospital Villarrica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>5637.91</v>
+        <v>3698.83</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1952-1225-CM26</t>
+          <t>608-7090-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2796,27 +2796,27 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.602.248-2</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hospital Villarrica</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>3721.91</v>
+        <v>3382.89</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1952-1368-CM26</t>
+          <t>1057501-5644-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2847,37 +2847,37 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.602.248-2</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hospital Villarrica</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>3613.2</v>
+        <v>2673.77</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>608-7090-CM26</t>
+          <t>812030-677-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,27 +2908,27 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>3367.6</v>
+        <v>8061.89</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1057501-5644-CM26</t>
+          <t>1057539-4675-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,37 +2969,37 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>HOSPITALIA Productos Medicos Ltda</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>2634.54</v>
+        <v>5542.87</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>812030-677-CM26</t>
+          <t>1057402-6584-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3040,27 +3040,27 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>7943.6</v>
+        <v>3859.73</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3378-5245-CM26</t>
+          <t>1057402-6581-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,27 +3101,27 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>3913.16</v>
+        <v>3859.73</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1057539-4675-CM26</t>
+          <t>1057402-6588-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3152,37 +3152,37 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>5504.87</v>
+        <v>3859.73</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1057402-6581-CM26</t>
+          <t>1057402-6577-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>3847.83</v>
+        <v>3859.73</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1057539-4657-CM26</t>
+          <t>1057402-6694-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3279,32 +3279,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>AETICA SPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
+          <t>77.535.386-4</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>13551.31</v>
+        <v>2528.71</v>
       </c>
     </row>
     <row r="48">
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>4027.91</v>
+        <v>4040.37</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1057402-6694-CM26</t>
+          <t>1057539-4657-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>AETICA SPA</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>77.535.386-4</t>
+          <t>78.874.470-6</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>2520.92</v>
+        <v>13593.2</v>
       </c>
     </row>
     <row r="50">
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>3951.81</v>
+        <v>3964.02</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1057402-6588-CM26</t>
+          <t>1057402-6571-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>3847.83</v>
+        <v>3859.73</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1057402-6584-CM26</t>
+          <t>1057402-6566-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>3847.83</v>
+        <v>4353.24</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1057402-6577-CM26</t>
+          <t>1057402-6569-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>3847.83</v>
+        <v>4439.84</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1057402-6571-CM26</t>
+          <t>1057402-6565-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>3847.83</v>
+        <v>3974.88</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1057402-6483-CM26</t>
+          <t>1057402-6564-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>7088.36</v>
+        <v>3859.73</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1057402-6566-CM26</t>
+          <t>1057402-6514-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>4339.83</v>
+        <v>4353.24</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1057402-6565-CM26</t>
+          <t>1057402-6510-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>3962.63</v>
+        <v>3859.73</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1057402-6564-CM26</t>
+          <t>1057402-6488-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>3847.83</v>
+        <v>3859.73</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1057402-6514-CM26</t>
+          <t>1057402-6485-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>4339.83</v>
+        <v>8393.73</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1057402-6510-CM26</t>
+          <t>1057402-6483-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>3847.83</v>
+        <v>7110.27</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1057402-6488-CM26</t>
+          <t>1549-2709-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4138,27 +4138,27 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>3847.83</v>
+        <v>28167.55</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1057402-6485-CM26</t>
+          <t>1549-2705-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4199,27 +4199,27 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>8367.860000000001</v>
+        <v>56085.87</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1057402-6569-CM26</t>
+          <t>1549-2707-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4260,27 +4260,27 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>4426.15</v>
+        <v>14604.29</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>68958.37</v>
+        <v>68775.98</v>
       </c>
     </row>
     <row r="65">
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>15065.08</v>
+        <v>15025.23</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1549-2705-CM26</t>
+          <t>608-7488-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4433,37 +4433,37 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>78.874.470-6</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>56234.6</v>
+        <v>2496.64</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1549-2707-CM26</t>
+          <t>1057539-4797-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4494,37 +4494,37 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>14643.02</v>
+        <v>61448.92</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1549-2709-CM26</t>
+          <t>812030-711-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4555,22 +4555,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>28242.24</v>
+        <v>6207.48</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1057539-4797-CM26</t>
+          <t>812030-613-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4616,27 +4616,27 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>62278.48</v>
+        <v>73062.75999999999</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>608-7488-CM26</t>
+          <t>1952-1616-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4687,27 +4687,27 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.602.248-2</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>Hospital Villarrica</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>2530.34</v>
+        <v>2348.71</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>812030-711-CM26</t>
+          <t>608-7409-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4738,37 +4738,37 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>6291.28</v>
+        <v>7749.94</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>5326-859-CM26</t>
+          <t>608-7503-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4809,27 +4809,27 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>GLOBALMED SPA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>76.400.383-7</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>15191.8</v>
+        <v>2397.13</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>608-7589-CM26</t>
+          <t>608-7505-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>ARENYS MED S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>76.901.400-4</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>5554.84</v>
+        <v>4240.14</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>608-7503-CM26</t>
+          <t>5326-859-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4931,27 +4931,27 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>GLOBALMED SPA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.400.383-7</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>2444.98</v>
+        <v>14894.44</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>608-7505-CM26</t>
+          <t>608-7589-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>ARENYS MED S.A.</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.901.400-4</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>4324.79</v>
+        <v>5446.11</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>608-7409-CM26</t>
+          <t>1057539-4912-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5043,37 +5043,37 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>7904.67</v>
+        <v>21889.66</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1952-1616-CM26</t>
+          <t>1057539-4865-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5114,27 +5114,27 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.602.248-2</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hospital Villarrica</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>GLOBALMED SPA</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.400.383-7</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>2395.6</v>
+        <v>18962.89</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>812030-613-CM26</t>
+          <t>1057539-4868-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5165,37 +5165,37 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.556.146-9</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>74521.42999999999</v>
+        <v>21607.58</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1057539-4865-CM26</t>
+          <t>1952-1685-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5236,27 +5236,27 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.602.248-2</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>Hospital Villarrica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>GLOBALMED SPA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>76.400.383-7</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>19248.06</v>
+        <v>75083.63</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1057539-4868-CM26</t>
+          <t>812030-712-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5287,37 +5287,37 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>21932.53</v>
+        <v>45337.65</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1057539-4912-CM26</t>
+          <t>1057539-4947-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>22218.85</v>
+        <v>54188.26</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1952-1685-CM26</t>
+          <t>5326-864-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5419,27 +5419,27 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.602.248-2</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hospital Villarrica</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.556.146-9</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>76659.10000000001</v>
+        <v>46479.34</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>812030-712-CM26</t>
+          <t>5326-865-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5475,32 +5475,32 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.556.146-9</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>46288.97</v>
+        <v>29971.27</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1057539-4947-CM26</t>
+          <t>2069-5526-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5526,42 +5526,42 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>55325.29</v>
+        <v>2346.16</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>5326-864-CM26</t>
+          <t>2069-5934-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5587,42 +5587,42 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>47454.61</v>
+        <v>3684.92</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>5326-865-CM26</t>
+          <t>2069-5912-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5648,42 +5648,42 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>30600.16</v>
+        <v>3491.07</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3378-5546-CM26</t>
+          <t>2069-5911-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>3533.06</v>
+        <v>5270.71</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1057539-5011-CM26</t>
+          <t>2069-5908-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5780,22 +5780,22 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>4449.84</v>
+        <v>12773.56</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2069-5934-CM26</t>
+          <t>2069-5525-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>3670.59</v>
+        <v>3513.8</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2069-5912-CM26</t>
+          <t>1057539-5011-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5902,22 +5902,22 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>3477.5</v>
+        <v>4467.21</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2069-5911-CM26</t>
+          <t>2069-5522-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>5250.21</v>
+        <v>3784.76</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2069-5908-CM26</t>
+          <t>2069-5517-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>12723.89</v>
+        <v>3491.07</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2069-5526-CM26</t>
+          <t>2069-5528-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>2337.04</v>
+        <v>5458.34</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2069-5525-CM26</t>
+          <t>5326-867-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6141,37 +6141,37 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>GLOBALMED SPA</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.400.383-7</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>3500.14</v>
+        <v>48316.94</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2069-5522-CM26</t>
+          <t>2069-6029-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>3770.04</v>
+        <v>3331.82</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2069-5517-CM26</t>
+          <t>2069-5521-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>3477.5</v>
+        <v>8091.56</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2069-5528-CM26</t>
+          <t>2069-6030-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>5437.12</v>
+        <v>7414.69</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>3378-5622-CM26</t>
+          <t>1057539-5169-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6385,27 +6385,27 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>4061.36</v>
+        <v>7720.45</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>5326-867-CM26</t>
+          <t>5326-869-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>GLOBALMED SPA</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>76.400.383-7</t>
+          <t>76.556.146-9</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>47835.83</v>
+        <v>38503.97</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2069-6030-CM26</t>
+          <t>5326-868-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6507,37 +6507,37 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.556.146-9</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>7341.18</v>
+        <v>17010.09</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2069-5521-CM26</t>
+          <t>812030-704-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6568,22 +6568,22 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6593,12 +6593,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>8011.34</v>
+        <v>10464.29</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2069-6029-CM26</t>
+          <t>1057049-15556-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6629,22 +6629,22 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>SINERMED SPA</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.367.671-4</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6669,13 +6669,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>3298.79</v>
+        <v>6736.87</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>812030-704-CM26</t>
+          <t>2069-5913-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6690,22 +6690,22 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -6730,13 +6730,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>10411.24</v>
+        <v>8758.370000000001</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>5326-868-CM26</t>
+          <t>1057539-5087-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6761,27 +6761,27 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>16923.85</v>
+        <v>3519.79</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>5326-869-CM26</t>
+          <t>1057402-7271-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6812,37 +6812,37 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -6852,13 +6852,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>38308.75</v>
+        <v>3714.9</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1057539-5169-CM26</t>
+          <t>1057402-7247-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6873,37 +6873,37 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -6913,13 +6913,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>7681.31</v>
+        <v>5836.56</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2069-5913-CM26</t>
+          <t>1057402-7245-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6944,27 +6944,27 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>8724.41</v>
+        <v>4273.24</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1057539-5087-CM26</t>
+          <t>1057402-7273-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6995,37 +6995,37 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>3506.14</v>
+        <v>5691.39</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1057402-7271-CM26</t>
+          <t>1057402-7196-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.556.146-9</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7096,13 +7096,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>3733.82</v>
+        <v>6414.13</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1057402-7273-CM26</t>
+          <t>1057402-7006-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7157,13 +7157,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>5720.37</v>
+        <v>7252.55</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1057402-7247-CM26</t>
+          <t>1057402-7241-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7218,13 +7218,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>5866.27</v>
+        <v>3714.9</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1057402-7241-CM26</t>
+          <t>1549-3011-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7239,27 +7239,27 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7279,13 +7279,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>3733.82</v>
+        <v>67653.86</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1057402-7196-CM26</t>
+          <t>2069-6189-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7310,27 +7310,27 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -7340,13 +7340,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>6446.79</v>
+        <v>10863.72</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1057402-7006-CM26</t>
+          <t>2069-6191-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7371,27 +7371,27 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -7401,13 +7401,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>7289.48</v>
+        <v>7561.02</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1057402-7245-CM26</t>
+          <t>2069-6352-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7432,27 +7432,27 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -7462,13 +7462,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>4295</v>
+        <v>4085.13</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1549-3011-CM26</t>
+          <t>2069-6356-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7483,22 +7483,22 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7508,12 +7508,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -7523,13 +7523,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>67215.66</v>
+        <v>13225.4</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2069-6189-CM26</t>
+          <t>1057539-5481-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7549,32 +7549,32 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>HOSPITALIA Productos Medicos Ltda</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K117" t="inlineStr"/>
@@ -7584,13 +7584,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>10838.87</v>
+        <v>3212.4</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2069-6191-CM26</t>
+          <t>1057501-7822-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7605,22 +7605,22 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -7645,13 +7645,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>7543.72</v>
+        <v>4117.74</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2069-6352-CM26</t>
+          <t>812030-753-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7666,22 +7666,22 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -7706,13 +7706,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>4075.79</v>
+        <v>4206.51</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2069-6356-CM26</t>
+          <t>1057501-7879-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -7767,13 +7767,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>13195.15</v>
+        <v>73393.87</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1057539-5481-CM26</t>
+          <t>1057402-7509-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7788,37 +7788,37 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -7828,13 +7828,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>3205.05</v>
+        <v>4197.93</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>3378-6046-CM26</t>
+          <t>1057402-7511-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7859,27 +7859,27 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -7889,13 +7889,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>4061.36</v>
+        <v>4281.44</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1057501-7822-CM26</t>
+          <t>1057402-7447-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7910,37 +7910,37 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -7950,13 +7950,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>4090.36</v>
+        <v>6323.65</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>3378-6087-CM26</t>
+          <t>1057402-7507-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7971,27 +7971,27 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8011,13 +8011,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>2683.93</v>
+        <v>3722.02</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>812030-753-CM26</t>
+          <t>608-7752-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8042,17 +8042,17 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8072,13 +8072,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>4177.28</v>
+        <v>47347.46</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1057402-7511-CM26</t>
+          <t>1057539-5660-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8093,37 +8093,37 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K126" t="inlineStr"/>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>4295</v>
+        <v>11661.69</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1057501-7879-CM26</t>
+          <t>1057501-7867-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8154,12 +8154,12 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K127" t="inlineStr"/>
@@ -8194,13 +8194,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>73626.42999999999</v>
+        <v>57603.57</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1057402-7509-CM26</t>
+          <t>1057501-7870-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -8225,27 +8225,27 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K128" t="inlineStr"/>
@@ -8255,13 +8255,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>4211.23</v>
+        <v>55218.01</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1057402-7507-CM26</t>
+          <t>1057501-7871-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8276,37 +8276,37 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K129" t="inlineStr"/>
@@ -8316,13 +8316,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>3733.82</v>
+        <v>27708.12</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1057402-7447-CM26</t>
+          <t>1057402-7716-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8337,7 +8337,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8362,12 +8362,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
@@ -8377,13 +8377,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>6343.69</v>
+        <v>3900.73</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>608-7752-CM26</t>
+          <t>812030-765-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8408,17 +8408,17 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8438,13 +8438,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>47450.7</v>
+        <v>10390.37</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1057539-5660-CM26</t>
+          <t>1057501-8128-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8459,7 +8459,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8469,27 +8469,27 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>78.566.250-4</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -8499,13 +8499,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>11687.12</v>
+        <v>20743.53</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1057501-7867-CM26</t>
+          <t>1057539-5748-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8520,37 +8520,37 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>78.874.470-6</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -8560,13 +8560,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>57719.28</v>
+        <v>71905.10000000001</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1057501-7870-CM26</t>
+          <t>1952-1929-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8581,37 +8581,37 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.602.248-2</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>Hospital Villarrica</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>GLOBALMED SPA</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.400.383-7</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -8621,13 +8621,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>55328.92</v>
+        <v>45477.7</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1057501-7871-CM26</t>
+          <t>608-7408-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8642,7 +8642,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8652,27 +8652,27 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>MEDYSSEY</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.485.678-3</t>
         </is>
       </c>
       <c r="K135" t="inlineStr"/>
@@ -8682,13 +8682,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>27763.77</v>
+        <v>4288.45</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1057402-7716-CM26</t>
+          <t>1549-3226-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8703,37 +8703,37 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K136" t="inlineStr"/>
@@ -8743,13 +8743,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>3908.56</v>
+        <v>67971.87</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>812030-765-CM26</t>
+          <t>1549-3291-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8789,12 +8789,12 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>HOSPITALIA Productos Medicos Ltda</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K137" t="inlineStr"/>
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>10411.24</v>
+        <v>3502.27</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1057501-8128-CM26</t>
+          <t>812030-776-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8825,22 +8825,22 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8850,12 +8850,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>78.566.250-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
@@ -8865,13 +8865,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>20785.19</v>
+        <v>45364.17</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1952-1929-CM26</t>
+          <t>2069-6712-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8886,7 +8886,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8896,27 +8896,27 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>61.602.248-2</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hospital Villarrica</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>GLOBALMED SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>76.400.383-7</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
@@ -8926,13 +8926,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>45742.47</v>
+        <v>5335.07</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1057539-5748-CM26</t>
+          <t>2069-6748-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -8957,27 +8957,27 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K140" t="inlineStr"/>
@@ -8987,13 +8987,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>72323.72</v>
+        <v>3500.77</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>608-7408-CM26</t>
+          <t>2069-6759-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -9018,27 +9018,27 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>MEDYSSEY</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>76.485.678-3</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K141" t="inlineStr"/>
@@ -9048,13 +9048,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>4358.79</v>
+        <v>3320.87</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1549-3226-CM26</t>
+          <t>1057501-8311-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9094,12 +9094,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>78.566.250-4</t>
         </is>
       </c>
       <c r="K142" t="inlineStr"/>
@@ -9109,13 +9109,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>69079.46000000001</v>
+        <v>6062.76</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>3378-6339-CM26</t>
+          <t>1549-3347-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9130,7 +9130,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -9140,12 +9140,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K143" t="inlineStr"/>
@@ -9170,13 +9170,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>2501.94</v>
+        <v>49721.66</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>812030-776-CM26</t>
+          <t>1057049-17208-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9186,42 +9186,42 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
@@ -9231,13 +9231,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>45617.07</v>
+        <v>66844.28999999999</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1549-3291-CM26</t>
+          <t>1057049-17118-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9247,42 +9247,42 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>SINERMED SPA</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>76.367.671-4</t>
         </is>
       </c>
       <c r="K145" t="inlineStr"/>
@@ -9292,13 +9292,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>3521.8</v>
+        <v>2883.93</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2069-6759-CM26</t>
+          <t>1057539-6078-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9308,12 +9308,12 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -9323,17 +9323,17 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t xml:space="preserve">Región de los Lagos </t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9353,13 +9353,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>3298.79</v>
+        <v>2782.86</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1057501-8311-CM26</t>
+          <t>1057402-8011-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9369,42 +9369,42 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región de Magallanes y de la Antártica</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>78.566.250-4</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K147" t="inlineStr"/>
@@ -9414,13 +9414,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>6022.45</v>
+        <v>3744.07</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2069-6712-CM26</t>
+          <t>1057402-7871-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9430,42 +9430,42 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
@@ -9475,13 +9475,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>5299.59</v>
+        <v>6470.64</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2069-6748-CM26</t>
+          <t>1057402-8189-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9491,42 +9491,42 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región de Magallanes y de la Antártica</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.556.146-9</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
@@ -9536,13 +9536,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>3477.5</v>
+        <v>7146.38</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1549-3347-CM26</t>
+          <t>1057402-8279-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9552,42 +9552,42 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
@@ -9597,7 +9597,2874 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>49391.07</v>
+        <v>3934.26</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>1057539-6141-CM26</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>TRIMED CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="n">
+        <v>34121.68</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>608-7765-CM26</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>61.606.602-1</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="n">
+        <v>62150.78</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>608-7790-CM26</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>61.606.602-1</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="n">
+        <v>13755.7</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>608-7804-CM26</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>61.606.602-1</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="n">
+        <v>73426.92</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2069-6703-CM26</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>61.608.101-2</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="n">
+        <v>7478.62</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2069-6762-CM26</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>61.608.101-2</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="n">
+        <v>5250.87</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2069-6959-CM26</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>61.608.101-2</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="n">
+        <v>9601.57</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2069-6962-CM26</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>61.608.101-2</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M158" s="2" t="n">
+        <v>5313.91</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>1057501-8921-CM26</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>61.608.502-6</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>DROGUERIA HOFMANN SAC</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="n">
+        <v>5742.68</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2069-6964-CM26</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>61.608.101-2</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="n">
+        <v>5446.38</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>608-9464-CM26</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>61.606.602-1</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>TARGET SITE CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>76.825.774-4</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="n">
+        <v>3529.14</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>608-9183-CM26</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>61.606.602-1</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>AETICA SPA</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>77.535.386-4</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M162" s="2" t="n">
+        <v>7190.38</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>812030-804-CM26</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>65.075.485-9</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="n">
+        <v>7690.35</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>812030-824-CM26</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>65.075.485-9</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="n">
+        <v>10599.79</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2069-7311-CM26</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>61.608.101-2</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="n">
+        <v>8498.540000000001</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>608-9546-CM26</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>61.606.602-1</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="n">
+        <v>15152.15</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>608-9697-CM26</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>61.606.602-1</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>AETICA SPA</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>77.535.386-4</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="n">
+        <v>2743.25</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>608-9704-CM26</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>61.606.602-1</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>ARENYS MED S.A.</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>76.901.400-4</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="n">
+        <v>6932.29</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>1549-3603-CM26</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>61.608.002-4</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="n">
+        <v>68447.7</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>1057402-8542-CM26</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>TARGET SITE CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>76.825.774-4</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="n">
+        <v>3980.3</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>1549-3602-CM26</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>61.608.002-4</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="n">
+        <v>73577.87</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>1057049-17460-CM26</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>61.608.604-9</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>BLUNDING S.A.</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>79.744.580-0</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="n">
+        <v>11343.41</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2069-7593-CM26</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>61.608.101-2</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="n">
+        <v>19069.59</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2069-7595-CM26</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>61.608.101-2</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="n">
+        <v>14853.23</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2069-7602-CM26</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>61.608.101-2</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="n">
+        <v>7578.59</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>812030-890-CM26</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>65.075.485-9</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="n">
+        <v>3722.5</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>1549-3689-CM26</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>61.608.002-4</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="n">
+        <v>56556.75</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>1057501-9565-CM26</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>61.608.502-6</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M178" s="2" t="n">
+        <v>46134.59</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>812030-798-CM26</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>65.075.485-9</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="n">
+        <v>5757.16</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>1057049-17479-CM26</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>61.608.604-9</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>TRIMED CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M180" s="2" t="n">
+        <v>3732.64</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>1057049-17540-CM26</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>61.608.604-9</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Medyssey</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>76.485.678-3</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M181" s="2" t="n">
+        <v>2358.69</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>1057402-8899-CM26</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>TRIMED CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M182" s="2" t="n">
+        <v>3749.65</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>812030-895-CM26</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>65.075.485-9</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="n">
+        <v>59644.5</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>1057539-6878-CM26</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>GLOBALMED SpA</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>76.400.383-7</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M184" s="2" t="n">
+        <v>60585.44</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>1952-2135-CM26</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>61.602.248-2</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Hospital Villarrica</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>78.566.250-4</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M185" s="2" t="n">
+        <v>14564.55</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>1952-2133-CM26</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>61.602.248-2</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Hospital Villarrica</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>78.566.250-4</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M186" s="2" t="n">
+        <v>5805.23</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>1057402-8592-CM26</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M187" s="2" t="n">
+        <v>3784.84</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>1057402-8334-CM26</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M188" s="2" t="n">
+        <v>5201.68</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>1057402-8508-CM26</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M189" s="2" t="n">
+        <v>5946.43</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>1057402-8336-CM26</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M190" s="2" t="n">
+        <v>4552.93</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>1057402-8322-CM26</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>TRIMED CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M191" s="2" t="n">
+        <v>2800.66</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>1057402-8511-CM26</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M192" s="2" t="n">
+        <v>4188.09</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>1549-3800-CM26</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>61.608.002-4</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M193" s="2" t="n">
+        <v>75746.94</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>1549-3801-CM26</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>61.608.002-4</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M194" s="2" t="n">
+        <v>69228.87</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>1952-2262-CM26</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>61.602.248-2</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Hospital Villarrica</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>78.566.250-4</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M195" s="2" t="n">
+        <v>15364.28</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>1549-3803-CM26</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>61.608.002-4</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M196" s="2" t="n">
+        <v>55550.71</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>1549-3804-CM26</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>61.608.002-4</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M197" s="2" t="n">
+        <v>9764.559999999999</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-top-organismos/endoprotesis-ortopedia-y-trauma.xlsx
+++ b/docs/oc-top-organismos/endoprotesis-ortopedia-y-trauma.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="endoprotesis-ort top org" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="endoprotesis-ort top org" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11773,7 +11773,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11956,7 +11956,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12322,7 +12322,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">

--- a/docs/oc-top-organismos/endoprotesis-ortopedia-y-trauma.xlsx
+++ b/docs/oc-top-organismos/endoprotesis-ortopedia-y-trauma.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M197"/>
+  <dimension ref="A1:M247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -819,7 +819,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1549-2076-CM26</t>
+          <t>1549-2085-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>33623.37</v>
+        <v>5040.29</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1549-2077-CM26</t>
+          <t>1549-2082-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>15123.24</v>
+        <v>28351.28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1549-2080-CM26</t>
+          <t>1549-2081-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>6761.2</v>
+        <v>56451.71</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1549-2081-CM26</t>
+          <t>1549-2077-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>56451.71</v>
+        <v>15123.24</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1549-2082-CM26</t>
+          <t>1549-2076-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>28351.28</v>
+        <v>33623.37</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1549-2085-CM26</t>
+          <t>1549-2080-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>5040.29</v>
+        <v>6761.2</v>
       </c>
     </row>
     <row r="13">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>GLOBALMED SPA</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1368,7 +1368,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2069-4170-CM26</t>
+          <t>2069-4280-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1429,7 +1429,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2069-4231-CM26</t>
+          <t>2069-4326-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>3597.72</v>
+        <v>7195.44</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2069-4233-CM26</t>
+          <t>2069-4234-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2069-4234-CM26</t>
+          <t>2069-4170-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1612,7 +1612,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2069-4280-CM26</t>
+          <t>2069-4231-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1673,7 +1673,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2069-4326-CM26</t>
+          <t>2069-4233-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>7195.44</v>
+        <v>3597.72</v>
       </c>
     </row>
     <row r="22">
@@ -1917,7 +1917,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1549-2292-CM26</t>
+          <t>812030-528-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>24082.25</v>
+        <v>4333.46</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>812030-528-CM26</t>
+          <t>1549-2292-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>4333.46</v>
+        <v>24082.25</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>812030-608-CM26</t>
+          <t>1057539-3987-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2064,27 +2064,27 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>46999.57</v>
+        <v>2778.87</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>812030-609-CM26</t>
+          <t>812030-608-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>36342.45</v>
+        <v>46999.57</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1057539-3987-CM26</t>
+          <t>812030-609-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2181,32 +2181,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2778.87</v>
+        <v>36342.45</v>
       </c>
     </row>
     <row r="30">
@@ -2588,7 +2588,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1952-1368-CM26</t>
+          <t>812030-669-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2613,27 +2613,27 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.602.248-2</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hospital Villarrica</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>3590.8</v>
+        <v>5602.96</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>812030-669-CM26</t>
+          <t>608-7090-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,17 +2674,17 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>5602.96</v>
+        <v>3382.89</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1952-1225-CM26</t>
+          <t>1057501-5644-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,37 +2725,37 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.602.248-2</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hospital Villarrica</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>3698.83</v>
+        <v>2673.77</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>608-7090-CM26</t>
+          <t>812030-677-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2786,27 +2786,27 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>3382.89</v>
+        <v>8061.89</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1057501-5644-CM26</t>
+          <t>1057539-4675-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2857,27 +2857,27 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>2673.77</v>
+        <v>5542.87</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>812030-677-CM26</t>
+          <t>1057539-4657-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,37 +2908,37 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>78.874.470-6</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>8061.89</v>
+        <v>13593.2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1057539-4675-CM26</t>
+          <t>1057402-6695-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,37 +2969,37 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>5542.87</v>
+        <v>4040.37</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1057402-6584-CM26</t>
+          <t>1057402-6694-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>AETICA SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>77.535.386-4</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>3859.73</v>
+        <v>2528.71</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1057402-6581-CM26</t>
+          <t>1057539-4560-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3101,27 +3101,27 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SINERMED SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.367.671-4</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>3859.73</v>
+        <v>3964.02</v>
       </c>
     </row>
     <row r="45">
@@ -3198,7 +3198,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1057402-6577-CM26</t>
+          <t>1057402-6584-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3259,7 +3259,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1057402-6694-CM26</t>
+          <t>1057402-6581-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>AETICA SPA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>77.535.386-4</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>2528.71</v>
+        <v>3859.73</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1057402-6695-CM26</t>
+          <t>1057402-6577-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>4040.37</v>
+        <v>3859.73</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1057539-4657-CM26</t>
+          <t>1057402-6571-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>13593.2</v>
+        <v>3859.73</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1057539-4560-CM26</t>
+          <t>1057402-6564-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3462,32 +3462,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>SINERMED SPA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.367.671-4</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>3964.02</v>
+        <v>3859.73</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1057402-6571-CM26</t>
+          <t>1057402-6566-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>3859.73</v>
+        <v>4353.24</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1057402-6566-CM26</t>
+          <t>1057402-6565-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>4353.24</v>
+        <v>3974.88</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1057402-6569-CM26</t>
+          <t>1057402-6514-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>4439.84</v>
+        <v>4353.24</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1057402-6565-CM26</t>
+          <t>1057402-6510-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>3974.88</v>
+        <v>3859.73</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1057402-6564-CM26</t>
+          <t>1057402-6488-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3808,7 +3808,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1057402-6514-CM26</t>
+          <t>1057402-6485-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>4353.24</v>
+        <v>8393.73</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1057402-6510-CM26</t>
+          <t>1057402-6483-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>3859.73</v>
+        <v>7110.27</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1057402-6488-CM26</t>
+          <t>1057402-6569-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>3859.73</v>
+        <v>4439.84</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1057402-6485-CM26</t>
+          <t>1549-2709-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4016,27 +4016,27 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>8393.73</v>
+        <v>28167.55</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1057402-6483-CM26</t>
+          <t>1549-2705-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4077,27 +4077,27 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>7110.27</v>
+        <v>56085.87</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1549-2709-CM26</t>
+          <t>1549-2707-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>28167.55</v>
+        <v>14604.29</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1549-2705-CM26</t>
+          <t>1549-2697-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>56085.87</v>
+        <v>68775.98</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1549-2707-CM26</t>
+          <t>1549-2703-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>14604.29</v>
+        <v>15025.23</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1549-2697-CM26</t>
+          <t>608-7488-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4311,37 +4311,37 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>78.874.470-6</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>68775.98</v>
+        <v>2496.64</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1549-2703-CM26</t>
+          <t>1057539-4797-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4372,37 +4372,37 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>15025.23</v>
+        <v>61448.92</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>608-7488-CM26</t>
+          <t>812030-711-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4443,27 +4443,27 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>2496.64</v>
+        <v>6207.48</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1057539-4797-CM26</t>
+          <t>812030-613-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4494,27 +4494,27 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>61448.92</v>
+        <v>73062.75999999999</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>812030-711-CM26</t>
+          <t>608-7409-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4555,37 +4555,37 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>6207.48</v>
+        <v>7749.94</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>812030-613-CM26</t>
+          <t>608-7503-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4621,32 +4621,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>73062.75999999999</v>
+        <v>2397.13</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1952-1616-CM26</t>
+          <t>608-7505-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4687,27 +4687,27 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.602.248-2</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hospital Villarrica</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>2348.71</v>
+        <v>4240.14</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>608-7409-CM26</t>
+          <t>5326-859-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>76.400.383-7</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>7749.94</v>
+        <v>14894.44</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>608-7503-CM26</t>
+          <t>608-7589-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>ARENYS MED S.A.</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.901.400-4</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2397.13</v>
+        <v>5446.11</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>608-7505-CM26</t>
+          <t>1057539-4912-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4870,27 +4870,27 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>4240.14</v>
+        <v>21889.66</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5326-859-CM26</t>
+          <t>2258-5366-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4921,37 +4921,37 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>GLOBALMED SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>76.400.383-7</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>14894.44</v>
+        <v>17511.89</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>608-7589-CM26</t>
+          <t>1057539-4865-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4992,27 +4992,27 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>ARENYS MED S.A.</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>76.901.400-4</t>
+          <t>76.400.383-7</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>5446.11</v>
+        <v>18962.89</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1057539-4912-CM26</t>
+          <t>1057539-4868-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.556.146-9</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>21889.66</v>
+        <v>21607.58</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1057539-4865-CM26</t>
+          <t>812030-712-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5104,37 +5104,37 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>GLOBALMED SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>76.400.383-7</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>18962.89</v>
+        <v>45337.65</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1057539-4868-CM26</t>
+          <t>1057539-4947-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>21607.58</v>
+        <v>54188.26</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1952-1685-CM26</t>
+          <t>5326-864-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5236,27 +5236,27 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.602.248-2</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hospital Villarrica</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.556.146-9</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>75083.63</v>
+        <v>46479.34</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>812030-712-CM26</t>
+          <t>5326-865-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5292,32 +5292,32 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.556.146-9</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>45337.65</v>
+        <v>29971.27</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1057539-4947-CM26</t>
+          <t>2258-5487-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5343,42 +5343,42 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SPINEX CORPORATION CHILE S.A</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.166.489-1</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>54188.26</v>
+        <v>9367.66</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5326-864-CM26</t>
+          <t>2069-5908-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5404,42 +5404,42 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>46479.34</v>
+        <v>12773.56</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5326-865-CM26</t>
+          <t>2069-5912-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5465,42 +5465,42 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>29971.27</v>
+        <v>3491.07</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2069-5526-CM26</t>
+          <t>2069-5911-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>2346.16</v>
+        <v>5270.71</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2069-5934-CM26</t>
+          <t>2069-5528-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>3684.92</v>
+        <v>5458.34</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2069-5912-CM26</t>
+          <t>2069-5934-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>3491.07</v>
+        <v>3684.92</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2069-5911-CM26</t>
+          <t>2069-5525-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>5270.71</v>
+        <v>3513.8</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2069-5908-CM26</t>
+          <t>2069-5522-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>12773.56</v>
+        <v>3784.76</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2069-5525-CM26</t>
+          <t>2069-5517-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>3513.8</v>
+        <v>3491.07</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1057539-5011-CM26</t>
+          <t>2069-5526-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5902,22 +5902,22 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>4467.21</v>
+        <v>2346.16</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2069-5522-CM26</t>
+          <t>1057539-5011-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5963,22 +5963,22 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>3784.76</v>
+        <v>4467.21</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2069-5517-CM26</t>
+          <t>5326-867-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6019,37 +6019,37 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.400.383-7</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>3491.07</v>
+        <v>48316.94</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2069-5528-CM26</t>
+          <t>2069-5521-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>5458.34</v>
+        <v>8091.56</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>5326-867-CM26</t>
+          <t>2069-6029-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6141,37 +6141,37 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>GLOBALMED SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>76.400.383-7</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>48316.94</v>
+        <v>3331.82</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2069-6029-CM26</t>
+          <t>2069-6030-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>3331.82</v>
+        <v>7414.69</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2069-5521-CM26</t>
+          <t>812030-704-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6288,12 +6288,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>8091.56</v>
+        <v>10464.29</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2069-6030-CM26</t>
+          <t>5326-868-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6324,37 +6324,37 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.556.146-9</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>7414.69</v>
+        <v>17010.09</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1057539-5169-CM26</t>
+          <t>5326-869-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6395,27 +6395,27 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.556.146-9</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>7720.45</v>
+        <v>38503.97</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>5326-869-CM26</t>
+          <t>1057539-5169-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6456,27 +6456,27 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>38503.97</v>
+        <v>7720.45</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>5326-868-CM26</t>
+          <t>1057049-15556-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6517,27 +6517,27 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>SINERMED SPA</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
+          <t>76.367.671-4</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>17010.09</v>
+        <v>6736.87</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>812030-704-CM26</t>
+          <t>2069-5913-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6568,22 +6568,22 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6593,12 +6593,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>10464.29</v>
+        <v>8758.370000000001</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1057049-15556-CM26</t>
+          <t>1057539-5087-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6639,27 +6639,27 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>SINERMED SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>76.367.671-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6669,13 +6669,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>6736.87</v>
+        <v>3519.79</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2069-5913-CM26</t>
+          <t>1057402-7273-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6700,27 +6700,27 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -6730,13 +6730,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>8758.370000000001</v>
+        <v>5691.39</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1057539-5087-CM26</t>
+          <t>1057402-7271-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6751,37 +6751,37 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>3519.79</v>
+        <v>3714.9</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1057402-7271-CM26</t>
+          <t>1057402-7247-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6852,13 +6852,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>3714.9</v>
+        <v>5836.56</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1057402-7247-CM26</t>
+          <t>1057402-7241-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6913,13 +6913,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>5836.56</v>
+        <v>3714.9</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1057402-7245-CM26</t>
+          <t>1057402-7196-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.556.146-9</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>4273.24</v>
+        <v>6414.13</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1057402-7273-CM26</t>
+          <t>1057402-7006-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>5691.39</v>
+        <v>7252.55</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1057402-7196-CM26</t>
+          <t>1057402-7245-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7096,13 +7096,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>6414.13</v>
+        <v>4273.24</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1057402-7006-CM26</t>
+          <t>1549-3011-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7117,27 +7117,27 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7157,13 +7157,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>7252.55</v>
+        <v>67653.86</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1057402-7241-CM26</t>
+          <t>2069-6189-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7188,27 +7188,27 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -7218,13 +7218,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>3714.9</v>
+        <v>10863.72</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1549-3011-CM26</t>
+          <t>2069-6191-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7239,22 +7239,22 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -7279,13 +7279,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>67653.86</v>
+        <v>7561.02</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2069-6189-CM26</t>
+          <t>2069-6352-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7340,13 +7340,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>10863.72</v>
+        <v>4085.13</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2069-6191-CM26</t>
+          <t>2069-6356-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7401,13 +7401,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>7561.02</v>
+        <v>13225.4</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2069-6352-CM26</t>
+          <t>1057539-5481-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7427,32 +7427,32 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -7462,13 +7462,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>4085.13</v>
+        <v>3212.4</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2069-6356-CM26</t>
+          <t>1057501-7822-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7483,22 +7483,22 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7508,12 +7508,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -7523,13 +7523,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>13225.4</v>
+        <v>4117.74</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1057539-5481-CM26</t>
+          <t>812030-753-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7544,7 +7544,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7554,27 +7554,27 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K117" t="inlineStr"/>
@@ -7584,13 +7584,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>3212.4</v>
+        <v>4206.51</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1057501-7822-CM26</t>
+          <t>1057402-7509-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7605,37 +7605,37 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -7645,13 +7645,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>4117.74</v>
+        <v>4197.93</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>812030-753-CM26</t>
+          <t>1057402-7511-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7666,37 +7666,37 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -7706,13 +7706,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>4206.51</v>
+        <v>4281.44</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1057501-7879-CM26</t>
+          <t>1057402-7447-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7732,32 +7732,32 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -7767,13 +7767,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>73393.87</v>
+        <v>6323.65</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1057402-7509-CM26</t>
+          <t>1057402-7507-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7828,13 +7828,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>4197.93</v>
+        <v>3722.02</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1057402-7511-CM26</t>
+          <t>1057501-7879-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7854,32 +7854,32 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -7889,13 +7889,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>4281.44</v>
+        <v>73393.87</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1057402-7447-CM26</t>
+          <t>1057539-5660-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7910,37 +7910,37 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -7950,13 +7950,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>6323.65</v>
+        <v>11661.69</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1057402-7507-CM26</t>
+          <t>608-7752-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7971,37 +7971,37 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -8011,13 +8011,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>3722.02</v>
+        <v>47347.46</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>608-7752-CM26</t>
+          <t>1057501-7867-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8032,37 +8032,37 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
@@ -8072,13 +8072,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>47347.46</v>
+        <v>57603.57</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1057539-5660-CM26</t>
+          <t>1057501-7870-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8093,27 +8093,27 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>11661.69</v>
+        <v>55218.01</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1057501-7867-CM26</t>
+          <t>1057501-7871-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8194,13 +8194,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>57603.57</v>
+        <v>27708.12</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1057501-7870-CM26</t>
+          <t>1057402-7716-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8225,27 +8225,27 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K128" t="inlineStr"/>
@@ -8255,13 +8255,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>55218.01</v>
+        <v>3900.73</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1057501-7871-CM26</t>
+          <t>812030-765-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8281,17 +8281,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K129" t="inlineStr"/>
@@ -8316,13 +8316,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>27708.12</v>
+        <v>10390.37</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1057402-7716-CM26</t>
+          <t>1057501-8128-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8342,32 +8342,32 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>78.566.250-4</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
@@ -8377,13 +8377,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>3900.73</v>
+        <v>20743.53</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>812030-765-CM26</t>
+          <t>1057539-5748-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8408,27 +8408,27 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>78.874.470-6</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -8438,13 +8438,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>10390.37</v>
+        <v>71905.10000000001</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1057501-8128-CM26</t>
+          <t>608-7408-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8459,7 +8459,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8469,27 +8469,27 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+          <t>Medyssey</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>78.566.250-4</t>
+          <t>76.485.678-3</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -8499,13 +8499,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>20743.53</v>
+        <v>4288.45</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1057539-5748-CM26</t>
+          <t>2258-6051-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8520,37 +8520,37 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -8560,13 +8560,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>71905.10000000001</v>
+        <v>3300.31</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1952-1929-CM26</t>
+          <t>1549-3226-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8591,27 +8591,27 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>61.602.248-2</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hospital Villarrica</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>GLOBALMED SPA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>76.400.383-7</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -8621,13 +8621,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>45477.7</v>
+        <v>67971.87</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>608-7408-CM26</t>
+          <t>1549-3291-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8642,7 +8642,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8652,27 +8652,27 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>MEDYSSEY</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>76.485.678-3</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K135" t="inlineStr"/>
@@ -8682,13 +8682,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>4288.45</v>
+        <v>3502.27</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1549-3226-CM26</t>
+          <t>812030-776-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8703,22 +8703,22 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8728,12 +8728,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K136" t="inlineStr"/>
@@ -8743,13 +8743,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>67971.87</v>
+        <v>45364.17</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1549-3291-CM26</t>
+          <t>2258-5681-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8764,37 +8764,37 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K137" t="inlineStr"/>
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>3502.27</v>
+        <v>10161.04</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>812030-776-CM26</t>
+          <t>2258-5597-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8835,17 +8835,17 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>45364.17</v>
+        <v>20449.55</v>
       </c>
     </row>
     <row r="139">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -9176,7 +9176,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1057049-17208-CM26</t>
+          <t>1057402-7871-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9196,22 +9196,22 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9231,13 +9231,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>66844.28999999999</v>
+        <v>6470.64</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1057049-17118-CM26</t>
+          <t>1057402-8011-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9262,27 +9262,27 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>SINERMED SPA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>76.367.671-4</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K145" t="inlineStr"/>
@@ -9292,13 +9292,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>2883.93</v>
+        <v>3744.07</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1057539-6078-CM26</t>
+          <t>1057402-8189-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9318,32 +9318,32 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.556.146-9</t>
         </is>
       </c>
       <c r="K146" t="inlineStr"/>
@@ -9353,13 +9353,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>2782.86</v>
+        <v>7146.38</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1057402-8011-CM26</t>
+          <t>1057049-17118-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9384,27 +9384,27 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SINERMED SPA</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.367.671-4</t>
         </is>
       </c>
       <c r="K147" t="inlineStr"/>
@@ -9414,13 +9414,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>3744.07</v>
+        <v>2883.93</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1057402-7871-CM26</t>
+          <t>1057049-17208-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9440,22 +9440,22 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9475,13 +9475,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>6470.64</v>
+        <v>66844.28999999999</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1057402-8189-CM26</t>
+          <t>1057539-6078-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9501,32 +9501,32 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
@@ -9536,13 +9536,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>7146.38</v>
+        <v>2782.86</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1057402-8279-CM26</t>
+          <t>1057539-6141-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9562,32 +9562,32 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>76.556.146-9</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
@@ -9597,13 +9597,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>3934.26</v>
+        <v>34121.68</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1057539-6141-CM26</t>
+          <t>1057402-8279-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9623,32 +9623,32 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -9658,13 +9658,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>34121.68</v>
+        <v>3934.26</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>608-7765-CM26</t>
+          <t>608-7804-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>62150.78</v>
+        <v>73426.92</v>
       </c>
     </row>
     <row r="153">
@@ -9786,7 +9786,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>608-7804-CM26</t>
+          <t>608-7765-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9826,12 +9826,12 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K154" t="inlineStr"/>
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>73426.92</v>
+        <v>62150.78</v>
       </c>
     </row>
     <row r="155">
@@ -10091,7 +10091,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1057501-8921-CM26</t>
+          <t>2069-6964-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10111,17 +10111,17 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10131,12 +10131,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
@@ -10146,13 +10146,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>5742.68</v>
+        <v>5446.38</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2069-6964-CM26</t>
+          <t>608-9464-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10177,27 +10177,27 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K160" t="inlineStr"/>
@@ -10207,13 +10207,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>5446.38</v>
+        <v>3529.14</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>608-9464-CM26</t>
+          <t>1057501-8921-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10233,32 +10233,32 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K161" t="inlineStr"/>
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>3529.14</v>
+        <v>5742.68</v>
       </c>
     </row>
     <row r="162">
@@ -10457,7 +10457,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2069-7311-CM26</t>
+          <t>1549-3603-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10477,17 +10477,17 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10497,12 +10497,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K165" t="inlineStr"/>
@@ -10512,13 +10512,13 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>8498.540000000001</v>
+        <v>68447.7</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>608-9546-CM26</t>
+          <t>608-9697-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10538,7 +10538,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -10558,12 +10558,12 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>AETICA SPA</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>77.535.386-4</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
@@ -10573,13 +10573,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>15152.15</v>
+        <v>2743.25</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>608-9697-CM26</t>
+          <t>608-9704-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10599,7 +10599,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>AETICA SPA</t>
+          <t>ARENYS MED S.A.</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>77.535.386-4</t>
+          <t>76.901.400-4</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
@@ -10634,13 +10634,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>2743.25</v>
+        <v>6932.29</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>608-9704-CM26</t>
+          <t>2069-7311-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10660,32 +10660,32 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>ARENYS MED S.A.</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>76.901.400-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K168" t="inlineStr"/>
@@ -10695,13 +10695,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>6932.29</v>
+        <v>8498.540000000001</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1549-3603-CM26</t>
+          <t>608-9546-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10726,17 +10726,17 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>68447.7</v>
+        <v>15152.15</v>
       </c>
     </row>
     <row r="170">
@@ -11311,7 +11311,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>812030-798-CM26</t>
+          <t>1057049-17540-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11336,12 +11336,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11351,12 +11351,12 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>Medyssey</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.485.678-3</t>
         </is>
       </c>
       <c r="K179" t="inlineStr"/>
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>5757.16</v>
+        <v>2358.69</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1057049-17479-CM26</t>
+          <t>812030-798-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11397,12 +11397,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11412,12 +11412,12 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K180" t="inlineStr"/>
@@ -11427,13 +11427,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>3732.64</v>
+        <v>5757.16</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1057049-17540-CM26</t>
+          <t>1057049-17479-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Medyssey</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>76.485.678-3</t>
+          <t>76.556.146-9</t>
         </is>
       </c>
       <c r="K181" t="inlineStr"/>
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>2358.69</v>
+        <v>3732.64</v>
       </c>
     </row>
     <row r="182">
@@ -11555,7 +11555,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>812030-895-CM26</t>
+          <t>2258-6605-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11570,7 +11570,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -11580,17 +11580,17 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11610,13 +11610,13 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>59644.5</v>
+        <v>5517.44</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1057539-6878-CM26</t>
+          <t>2258-6314-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11631,37 +11631,37 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>GLOBALMED SpA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>76.400.383-7</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K184" t="inlineStr"/>
@@ -11671,13 +11671,13 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>60585.44</v>
+        <v>22308.77</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1952-2135-CM26</t>
+          <t>2258-6335-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11692,37 +11692,37 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>61.602.248-2</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Hospital Villarrica</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>78.566.250-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K185" t="inlineStr"/>
@@ -11732,13 +11732,13 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>14564.55</v>
+        <v>60794</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1952-2133-CM26</t>
+          <t>812030-895-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11753,37 +11753,37 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>61.602.248-2</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Hospital Villarrica</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>78.566.250-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K186" t="inlineStr"/>
@@ -11793,13 +11793,13 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>5805.23</v>
+        <v>59644.5</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1057402-8592-CM26</t>
+          <t>1057402-8322-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.556.146-9</t>
         </is>
       </c>
       <c r="K187" t="inlineStr"/>
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>3784.84</v>
+        <v>2800.66</v>
       </c>
     </row>
     <row r="188">
@@ -11921,7 +11921,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1057402-8508-CM26</t>
+          <t>1057402-8336-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11976,13 +11976,13 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>5946.43</v>
+        <v>4552.93</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1057402-8336-CM26</t>
+          <t>1057402-8508-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12037,13 +12037,13 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>4552.93</v>
+        <v>5946.43</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1057402-8322-CM26</t>
+          <t>1057402-8511-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K191" t="inlineStr"/>
@@ -12098,13 +12098,13 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>2800.66</v>
+        <v>4188.09</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1057402-8511-CM26</t>
+          <t>1057402-8592-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12159,13 +12159,13 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>4188.09</v>
+        <v>3784.84</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>1549-3800-CM26</t>
+          <t>1057539-6878-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12180,37 +12180,37 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.400.383-7</t>
         </is>
       </c>
       <c r="K193" t="inlineStr"/>
@@ -12220,13 +12220,13 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>75746.94</v>
+        <v>60585.44</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1549-3801-CM26</t>
+          <t>1549-3800-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12266,12 +12266,12 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K194" t="inlineStr"/>
@@ -12281,13 +12281,13 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>69228.87</v>
+        <v>75746.94</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>1952-2262-CM26</t>
+          <t>1549-3801-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12307,32 +12307,32 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>61.602.248-2</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Hospital Villarrica</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>78.566.250-4</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K195" t="inlineStr"/>
@@ -12342,13 +12342,13 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>15364.28</v>
+        <v>69228.87</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1549-3803-CM26</t>
+          <t>1549-3804-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12403,13 +12403,13 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>55550.71</v>
+        <v>9764.559999999999</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1549-3804-CM26</t>
+          <t>1549-3803-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12464,7 +12464,3057 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>9764.559999999999</v>
+        <v>55550.71</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>608-9958-CM26</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>61.606.602-1</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>TARGET SITE CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>76.825.774-4</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M198" s="2" t="n">
+        <v>2651.81</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>1057402-8807-CM26</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M199" s="2" t="n">
+        <v>3710.34</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>1057402-8811-CM26</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M200" s="2" t="n">
+        <v>4105.65</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>1057402-8818-CM26</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M201" s="2" t="n">
+        <v>5892.31</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>1057402-8820-CM26</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M202" s="2" t="n">
+        <v>3710.34</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>1057402-9135-CM26</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M203" s="2" t="n">
+        <v>4463.31</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>1057539-7181-CM26</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>BIOIMPLANTES SA</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>76.214.144-2</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M204" s="2" t="n">
+        <v>12315.46</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>1057539-7216-CM26</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M205" s="2" t="n">
+        <v>76374.17999999999</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>1057539-7288-CM26</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>TRIMED CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M206" s="2" t="n">
+        <v>7601.14</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>1057539-7289-CM26</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M207" s="2" t="n">
+        <v>74730.62</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>5326-1217-CM26</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>61.602.140-0</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>GLOBALMED SpA</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>76.400.383-7</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M208" s="2" t="n">
+        <v>38166.18</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>1057539-7405-CM26</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr"/>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M209" s="2" t="n">
+        <v>72780.28</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>1057539-7408-CM26</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>TRIMED CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M210" s="2" t="n">
+        <v>5088.08</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>1057501-10358-CM26</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>61.608.502-6</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>DROGUERIA HOFMANN SAC</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr"/>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M211" s="2" t="n">
+        <v>6626.54</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>1549-3809-CM26</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>61.608.002-4</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M212" s="2" t="n">
+        <v>2599.64</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2258-7186-CM26</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>61.606.201-8</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M213" s="2" t="n">
+        <v>22225.28</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>608-10990-CM26</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>61.606.602-1</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>AETICA SPA</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>77.535.386-4</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr"/>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M214" s="2" t="n">
+        <v>2942.39</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>1057539-7406-CM26</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr"/>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M215" s="2" t="n">
+        <v>67456.19</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>1057539-7407-CM26</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr"/>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M216" s="2" t="n">
+        <v>55324.51</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>1057539-7572-CM26</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>BIOIMPLANTES SA</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>76.214.144-2</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr"/>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M217" s="2" t="n">
+        <v>7299.34</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>1549-4039-CM26</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>61.608.002-4</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>SINERMED SPA</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>76.367.671-4</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr"/>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M218" s="2" t="n">
+        <v>7237.75</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>1057539-7603-CM26</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr"/>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M219" s="2" t="n">
+        <v>5041.03</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>1057539-7619-CM26</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>BIOIMPLANTES SA</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>76.214.144-2</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr"/>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M220" s="2" t="n">
+        <v>72993.36</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>1057049-18220-CM26</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>61.608.604-9</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr"/>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M221" s="2" t="n">
+        <v>74059.52</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>812030-917-CM26</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>65.075.485-9</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr"/>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M222" s="2" t="n">
+        <v>10301.25</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>1057539-7692-CM26</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>OSTEOTRAUMA SPA</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>76.965.562-K</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr"/>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M223" s="2" t="n">
+        <v>16694.48</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2258-7398-CM26</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>61.606.201-8</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr"/>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M224" s="2" t="n">
+        <v>18783.26</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>1549-4107-CM26</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>61.608.002-4</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr"/>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M225" s="2" t="n">
+        <v>73125.41</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>1549-4099-CM26</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>61.608.002-4</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr"/>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M226" s="2" t="n">
+        <v>10310.62</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>1057501-10748-CM26</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>61.608.502-6</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr"/>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M227" s="2" t="n">
+        <v>38997.52</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>1057402-9564-CM26</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>TRIMED CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr"/>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M228" s="2" t="n">
+        <v>5336.51</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>1057049-17695-CM26</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>61.608.604-9</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr"/>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M229" s="2" t="n">
+        <v>6345.23</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>1057501-10834-CM26</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>61.608.502-6</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>78.566.250-4</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr"/>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M230" s="2" t="n">
+        <v>15194.46</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>1057539-7898-CM26</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr"/>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M231" s="2" t="n">
+        <v>28598.42</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>1057049-18545-CM26</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>61.608.604-9</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>BIOIMPLANTES SA</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>76.214.144-2</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M232" s="2" t="n">
+        <v>62230.66</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>1057539-7998-CM26</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>TRIMED CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr"/>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M233" s="2" t="n">
+        <v>7430.79</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>1057539-8024-CM26</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>SINERMED SPA</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>76.367.671-4</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr"/>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M234" s="2" t="n">
+        <v>28095.39</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>1057539-7411-CM26</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr"/>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M235" s="2" t="n">
+        <v>64519.04</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>1057539-8032-CM26</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>TARGET SITE CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>76.825.774-4</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr"/>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M236" s="2" t="n">
+        <v>12096.26</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>1057539-8040-CM26</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>TARGET SITE CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>76.825.774-4</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M237" s="2" t="n">
+        <v>12096.26</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>608-11651-CM26</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>61.606.602-1</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M238" s="2" t="n">
+        <v>18524.55</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>608-11665-CM26</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>61.606.602-1</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr"/>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M239" s="2" t="n">
+        <v>2870.44</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>812030-974-CM26</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>65.075.485-9</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M240" s="2" t="n">
+        <v>4383.67</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>1549-4205-CM26</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>61.608.002-4</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr"/>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M241" s="2" t="n">
+        <v>72274.78</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>1057402-10002-CM26</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>TRIMED CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr"/>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M242" s="2" t="n">
+        <v>4873.15</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>1057402-10037-CM26</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr"/>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M243" s="2" t="n">
+        <v>4312.16</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>1057539-8097-CM26</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>DROGUERIA HOFMANN SAC</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr"/>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M244" s="2" t="n">
+        <v>2341.47</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>812030-953-CM26</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>65.075.485-9</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr"/>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M245" s="2" t="n">
+        <v>40858.64</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>812030-952-CM26</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>65.075.485-9</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr"/>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M246" s="2" t="n">
+        <v>40018.36</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>1057539-8154-CM26</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>SINERMED SPA</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>76.367.671-4</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr"/>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M247" s="2" t="n">
+        <v>5518</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-top-organismos/endoprotesis-ortopedia-y-trauma.xlsx
+++ b/docs/oc-top-organismos/endoprotesis-ortopedia-y-trauma.xlsx
@@ -684,7 +684,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1908,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2034,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2099,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2774,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2900,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +2965,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3091,11 @@
           <t>77.535.386-4</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4376,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5112,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5299,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5364,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6405,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6470,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7023,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7515,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7580,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8499,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +8625,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +8751,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9426,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +9674,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10349,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10414,11 @@
           <t>77.535.386-4</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +10662,11 @@
           <t>77.535.386-4</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11032,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +11585,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +11650,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +11959,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13122,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +13370,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +13435,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13372,7 +13500,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +13626,11 @@
           <t>77.535.386-4</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13799,7 +13935,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +14488,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +14797,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15202,7 +15350,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15324,7 +15476,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-top-organismos/endoprotesis-ortopedia-y-trauma.xlsx
+++ b/docs/oc-top-organismos/endoprotesis-ortopedia-y-trauma.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M233"/>
+  <dimension ref="A1:M235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -5652,7 +5652,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5326-868-CM26</t>
+          <t>812030-704-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5672,32 +5672,32 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5711,13 +5711,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>17010.09</v>
+        <v>10464.29</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>812030-704-CM26</t>
+          <t>5326-868-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5742,27 +5742,27 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.556.146-9</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5776,7 +5776,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>10464.29</v>
+        <v>17010.09</v>
       </c>
     </row>
     <row r="86">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -6270,7 +6270,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1057539-5481-CM26</t>
+          <t>2069-6356-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6290,52 +6290,48 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>3212.4</v>
+        <v>13225.4</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2069-6356-CM26</t>
+          <t>1057539-5481-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6360,37 +6356,41 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>13225.4</v>
+        <v>3212.4</v>
       </c>
     </row>
     <row r="96">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -6591,7 +6591,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1057539-5660-CM26</t>
+          <t>608-7752-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6611,48 +6611,52 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>11661.69</v>
+        <v>47347.46</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>608-7752-CM26</t>
+          <t>1057539-5660-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6672,46 +6676,42 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>47347.46</v>
+        <v>11661.69</v>
       </c>
     </row>
     <row r="101">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -6778,7 +6778,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1057501-7871-CM26</t>
+          <t>812030-765-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6803,12 +6803,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6818,28 +6818,32 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>27708.12</v>
+        <v>10390.37</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1057501-7870-CM26</t>
+          <t>1057501-7871-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6894,13 +6898,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>55218.01</v>
+        <v>27708.12</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1057501-7867-CM26</t>
+          <t>1057501-7870-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6955,13 +6959,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>57603.57</v>
+        <v>55218.01</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>812030-765-CM26</t>
+          <t>1057501-7867-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6986,12 +6990,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -7001,26 +7005,22 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>10390.37</v>
+        <v>57603.57</v>
       </c>
     </row>
     <row r="106">
@@ -7152,7 +7152,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2258-6051-CM26</t>
+          <t>1549-3226-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7177,47 +7177,43 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>3300.31</v>
+        <v>67971.87</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1549-3226-CM26</t>
+          <t>2258-6051-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7237,42 +7233,46 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr"/>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>67971.87</v>
+        <v>3300.31</v>
       </c>
     </row>
     <row r="110">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -7526,7 +7526,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2069-6712-CM26</t>
+          <t>1549-3347-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7546,17 +7546,17 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7566,28 +7566,32 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>5335.07</v>
+        <v>49721.66</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2069-6748-CM26</t>
+          <t>2069-6759-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7607,7 +7611,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -7642,13 +7646,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>3500.77</v>
+        <v>3320.87</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2069-6759-CM26</t>
+          <t>2069-6748-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7668,7 +7672,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -7703,13 +7707,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>3320.87</v>
+        <v>3500.77</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1549-3347-CM26</t>
+          <t>2069-6712-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7729,17 +7733,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7749,26 +7753,22 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>49721.66</v>
+        <v>5335.07</v>
       </c>
     </row>
     <row r="118">
@@ -7835,7 +7835,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1057049-17118-CM26</t>
+          <t>1057049-17208-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7875,12 +7875,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>SINERMED SPA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>76.367.671-4</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -7890,13 +7890,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>2883.93</v>
+        <v>66844.28999999999</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1057049-17208-CM26</t>
+          <t>1057539-6078-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7921,27 +7921,27 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -7951,13 +7951,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>66844.28999999999</v>
+        <v>2782.86</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1057539-6078-CM26</t>
+          <t>1057049-17118-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7977,32 +7977,32 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>SINERMED SPA</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.367.671-4</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -8012,7 +8012,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>2782.86</v>
+        <v>2883.93</v>
       </c>
     </row>
     <row r="122">
@@ -8290,7 +8290,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -8351,7 +8351,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -8412,7 +8412,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -8473,7 +8473,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -8514,7 +8514,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1057501-8921-CM26</t>
+          <t>608-9464-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8534,52 +8534,48 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.825.774-4</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>5742.68</v>
+        <v>3529.14</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>608-9464-CM26</t>
+          <t>1057501-8921-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8599,42 +8595,46 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr"/>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>3529.14</v>
+        <v>5742.68</v>
       </c>
     </row>
     <row r="132">
@@ -8831,7 +8831,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>812030-824-CM26</t>
+          <t>1057417-14921-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8851,52 +8851,48 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SPINEX CORPORATION CHILE S.A</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.166.489-1</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>10599.79</v>
+        <v>41743.24</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1057417-14921-CM26</t>
+          <t>812030-824-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8916,48 +8912,52 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>SPINEX CORPORATION CHILE S.A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>76.166.489-1</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>41743.24</v>
+        <v>10599.79</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2069-7311-CM26</t>
+          <t>608-9697-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8982,43 +8982,47 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>AETICA SPA</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr"/>
+          <t>77.535.386-4</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>8498.540000000001</v>
+        <v>2743.25</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>608-9546-CM26</t>
+          <t>608-9704-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9058,12 +9062,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>ARENYS MED S.A.</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.901.400-4</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
@@ -9073,13 +9077,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>15152.15</v>
+        <v>6932.29</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>608-9697-CM26</t>
+          <t>1549-3603-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9104,47 +9108,43 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>AETICA SPA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>77.535.386-4</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>2743.25</v>
+        <v>68447.7</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>608-9704-CM26</t>
+          <t>2069-7311-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9164,32 +9164,32 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>ARENYS MED S.A.</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>76.901.400-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K140" t="inlineStr"/>
@@ -9199,13 +9199,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>6932.29</v>
+        <v>8498.540000000001</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1549-3603-CM26</t>
+          <t>608-9546-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9230,17 +9230,17 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9260,13 +9260,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>68447.7</v>
+        <v>15152.15</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1549-3602-CM26</t>
+          <t>1057539-6536-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9281,57 +9281,53 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>99.585.860-6</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>73577.87</v>
+        <v>3583.75</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1057049-17460-CM26</t>
+          <t>1549-3602-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9346,7 +9342,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -9356,12 +9352,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9371,12 +9367,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>BLUNDING S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>79.744.580-0</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -9390,13 +9386,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>11343.41</v>
+        <v>73577.87</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2069-7593-CM26</t>
+          <t>1057049-17460-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9411,7 +9407,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -9421,12 +9417,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9436,28 +9432,32 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BLUNDING S.A.</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr"/>
+          <t>79.744.580-0</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>19069.59</v>
+        <v>11343.41</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2069-7602-CM26</t>
+          <t>2069-7593-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9477,7 +9477,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -9512,7 +9512,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>7578.59</v>
+        <v>19069.59</v>
       </c>
     </row>
     <row r="146">
@@ -9579,7 +9579,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>812030-890-CM26</t>
+          <t>2069-7602-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9594,7 +9594,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -9604,12 +9604,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9619,32 +9619,28 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>3722.5</v>
+        <v>7578.59</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1549-3689-CM26</t>
+          <t>812030-890-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9664,17 +9660,17 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9684,28 +9680,32 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>56556.75</v>
+        <v>3722.5</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1057501-9565-CM26</t>
+          <t>1549-3689-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9730,12 +9730,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9745,12 +9745,12 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
@@ -9760,13 +9760,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>46134.59</v>
+        <v>56556.75</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>812030-798-CM26</t>
+          <t>1057501-9565-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9781,22 +9781,22 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9806,12 +9806,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
@@ -9821,13 +9821,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>5757.16</v>
+        <v>46134.59</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1057049-17479-CM26</t>
+          <t>812030-798-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9847,17 +9847,17 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9867,32 +9867,28 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>3732.64</v>
+        <v>5757.16</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1057049-17540-CM26</t>
+          <t>1057049-17479-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9932,28 +9928,32 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Medyssey</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>76.485.678-3</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr"/>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>2358.69</v>
+        <v>3732.64</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2258-6605-CM26</t>
+          <t>1057049-17540-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -9978,27 +9978,27 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>Medyssey</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.485.678-3</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -10008,13 +10008,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>5517.44</v>
+        <v>2358.69</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2258-6335-CM26</t>
+          <t>2258-6314-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -10069,13 +10069,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>60794</v>
+        <v>22308.77</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2258-6314-CM26</t>
+          <t>2258-6605-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -10130,13 +10130,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>22308.77</v>
+        <v>5517.44</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>812030-895-CM26</t>
+          <t>2258-6335-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -10151,7 +10151,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -10161,17 +10161,17 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10191,13 +10191,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>59644.5</v>
+        <v>60794</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1057539-6878-CM26</t>
+          <t>812030-895-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10212,37 +10212,37 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>GLOBALMED SpA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>76.400.383-7</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>60585.44</v>
+        <v>59644.5</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1549-3800-CM26</t>
+          <t>1057417-14576-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -10283,27 +10283,27 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>99.585.860-6</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -10313,13 +10313,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>75746.94</v>
+        <v>8292.5</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1549-3801-CM26</t>
+          <t>1057539-6878-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10334,57 +10334,53 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.400.383-7</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>69228.87</v>
+        <v>60585.44</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1549-3804-CM26</t>
+          <t>1549-3800-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10399,12 +10395,12 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -10424,32 +10420,28 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>9764.559999999999</v>
+        <v>75746.94</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1549-3803-CM26</t>
+          <t>1549-3801-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10464,12 +10456,12 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -10508,13 +10500,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>55550.71</v>
+        <v>69228.87</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>608-9958-CM26</t>
+          <t>1549-3804-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10524,58 +10516,62 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>2651.81</v>
+        <v>9764.559999999999</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1057539-7181-CM26</t>
+          <t>1549-3803-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10585,58 +10581,62 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>BIOIMPLANTES SA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>76.214.144-2</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>12315.46</v>
+        <v>55550.71</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1057539-7216-CM26</t>
+          <t>608-9958-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10651,37 +10651,37 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K164" t="inlineStr"/>
@@ -10691,13 +10691,13 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>76374.17999999999</v>
+        <v>2651.81</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1057539-7287-CM26</t>
+          <t>1057539-7216-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10712,7 +10712,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>TECNOMEDICAL S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>99.585.860-6</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K165" t="inlineStr"/>
@@ -10752,13 +10752,13 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>54179.57</v>
+        <v>76374.17999999999</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1057539-7288-CM26</t>
+          <t>1057539-7181-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10773,7 +10773,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -10798,32 +10798,28 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>BIOIMPLANTES SA</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.214.144-2</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>7601.14</v>
+        <v>12315.46</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1057539-7289-CM26</t>
+          <t>1057539-7287-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10863,12 +10859,12 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>99.585.860-6</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
@@ -10878,13 +10874,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>74730.62</v>
+        <v>54179.57</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1057539-7290-CM26</t>
+          <t>1057539-7288-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10924,28 +10920,32 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>TECNOMEDICAL S A</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>99.585.860-6</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr"/>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>66609</v>
+        <v>7601.14</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>5326-1217-CM26</t>
+          <t>1057539-7289-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10970,27 +10970,27 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>GLOBALMED SpA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>76.400.383-7</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K169" t="inlineStr"/>
@@ -11000,13 +11000,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>38166.18</v>
+        <v>74730.62</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1057539-7405-CM26</t>
+          <t>1057539-7290-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11021,7 +11021,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -11046,12 +11046,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>99.585.860-6</t>
         </is>
       </c>
       <c r="K170" t="inlineStr"/>
@@ -11061,13 +11061,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>72780.28</v>
+        <v>66609</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1057539-7408-CM26</t>
+          <t>5326-1217-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -11092,47 +11092,43 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.400.383-7</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>5088.08</v>
+        <v>38166.18</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1057501-10358-CM26</t>
+          <t>1057539-7405-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11147,57 +11143,53 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
-        </is>
-      </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>6626.54</v>
+        <v>72780.28</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1549-3809-CM26</t>
+          <t>1057539-7408-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11212,37 +11204,37 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>76.556.146-9</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -11256,13 +11248,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>2599.64</v>
+        <v>5088.08</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2258-7186-CM26</t>
+          <t>1549-3809-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11277,7 +11269,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -11287,43 +11279,47 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K174" t="inlineStr"/>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>22225.28</v>
+        <v>2599.64</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>608-10990-CM26</t>
+          <t>1057501-10358-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11338,7 +11334,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -11348,27 +11344,27 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>AETICA SPA</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>77.535.386-4</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -11382,13 +11378,13 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>2942.39</v>
+        <v>6626.54</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1057049-18220-CM26</t>
+          <t>2258-7186-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11403,7 +11399,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -11413,27 +11409,27 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K176" t="inlineStr"/>
@@ -11443,13 +11439,13 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>74059.52</v>
+        <v>22225.28</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1057539-7406-CM26</t>
+          <t>608-10990-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11464,53 +11460,57 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>AETICA SPA</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr"/>
+          <t>77.535.386-4</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>67456.19</v>
+        <v>2942.39</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1057539-7407-CM26</t>
+          <t>1057539-7406-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11565,13 +11565,13 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>55324.51</v>
+        <v>67456.19</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1057539-7572-CM26</t>
+          <t>1057539-7407-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -11611,12 +11611,12 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>BIOIMPLANTES SA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>76.214.144-2</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K179" t="inlineStr"/>
@@ -11626,13 +11626,13 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>7299.34</v>
+        <v>55324.51</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1549-4039-CM26</t>
+          <t>1057539-7572-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11652,32 +11652,32 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>SINERMED SPA</t>
+          <t>BIOIMPLANTES SA</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>76.367.671-4</t>
+          <t>76.214.144-2</t>
         </is>
       </c>
       <c r="K180" t="inlineStr"/>
@@ -11687,13 +11687,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>7237.75</v>
+        <v>7299.34</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1057539-7619-CM26</t>
+          <t>1549-4039-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11713,32 +11713,32 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>BIOIMPLANTES SA</t>
+          <t>SINERMED SPA</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>76.214.144-2</t>
+          <t>76.367.671-4</t>
         </is>
       </c>
       <c r="K181" t="inlineStr"/>
@@ -11748,7 +11748,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>72993.36</v>
+        <v>7237.75</v>
       </c>
     </row>
     <row r="182">
@@ -11819,7 +11819,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>812030-917-CM26</t>
+          <t>1057539-7619-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -11844,47 +11844,43 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>BIOIMPLANTES SA</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.214.144-2</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>10301.25</v>
+        <v>72993.36</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1057539-7692-CM26</t>
+          <t>1057049-18220-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11899,37 +11895,37 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>OSTEOTRAUMA SPA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>76.965.562-K</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K184" t="inlineStr"/>
@@ -11939,13 +11935,13 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>16694.48</v>
+        <v>74059.52</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2258-7398-CM26</t>
+          <t>1057539-7692-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11960,37 +11956,37 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>OSTEOTRAUMA SPA</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.965.562-K</t>
         </is>
       </c>
       <c r="K185" t="inlineStr"/>
@@ -12000,13 +11996,13 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>18783.26</v>
+        <v>16694.48</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1549-4099-CM26</t>
+          <t>812030-917-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -12021,22 +12017,22 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -12046,28 +12042,32 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
-        </is>
-      </c>
-      <c r="K186" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>10310.62</v>
+        <v>10301.25</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1057049-17695-CM26</t>
+          <t>2258-7398-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -12082,7 +12082,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -12092,17 +12092,17 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -12122,13 +12122,13 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>6345.23</v>
+        <v>18783.26</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1549-4107-CM26</t>
+          <t>1057049-17695-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12153,12 +12153,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -12168,12 +12168,12 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K188" t="inlineStr"/>
@@ -12183,13 +12183,13 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>73125.41</v>
+        <v>6345.23</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1057501-10748-CM26</t>
+          <t>1549-4107-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12214,12 +12214,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -12229,12 +12229,12 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K189" t="inlineStr"/>
@@ -12244,13 +12244,13 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>38997.52</v>
+        <v>73125.41</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1057417-15577-CM26</t>
+          <t>1057501-10748-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12265,7 +12265,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -12275,17 +12275,17 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12305,13 +12305,13 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>34172.86</v>
+        <v>38997.52</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1057417-15578-CM26</t>
+          <t>1549-4099-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12326,7 +12326,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -12336,27 +12336,27 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>TECNOMEDICAL S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>99.585.860-6</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K191" t="inlineStr"/>
@@ -12366,13 +12366,13 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>3000</v>
+        <v>10310.62</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1057417-15864-CM26</t>
+          <t>1057417-15577-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12392,7 +12392,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -12412,12 +12412,12 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>TECNOMEDICAL S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>99.585.860-6</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K192" t="inlineStr"/>
@@ -12427,13 +12427,13 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>16875</v>
+        <v>34172.86</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>1057501-10834-CM26</t>
+          <t>1057417-15578-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12453,32 +12453,32 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>78.566.250-4</t>
+          <t>99.585.860-6</t>
         </is>
       </c>
       <c r="K193" t="inlineStr"/>
@@ -12488,13 +12488,13 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>15194.46</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1057539-7898-CM26</t>
+          <t>1057417-15864-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -12519,27 +12519,27 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>99.585.860-6</t>
         </is>
       </c>
       <c r="K194" t="inlineStr"/>
@@ -12549,13 +12549,13 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>28598.42</v>
+        <v>16875</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>1057049-18545-CM26</t>
+          <t>1057501-10834-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12570,7 +12570,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12595,12 +12595,12 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>BIOIMPLANTES SA</t>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>76.214.144-2</t>
+          <t>78.566.250-4</t>
         </is>
       </c>
       <c r="K195" t="inlineStr"/>
@@ -12610,7 +12610,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>62230.66</v>
+        <v>15194.46</v>
       </c>
     </row>
     <row r="196">
@@ -12681,7 +12681,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1057539-8024-CM26</t>
+          <t>1057539-7898-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12696,7 +12696,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -12721,12 +12721,12 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>SINERMED SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>76.367.671-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K197" t="inlineStr"/>
@@ -12736,13 +12736,13 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>28095.39</v>
+        <v>28598.42</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1057539-7411-CM26</t>
+          <t>1057049-18545-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12757,37 +12757,37 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOIMPLANTES SA</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.214.144-2</t>
         </is>
       </c>
       <c r="K198" t="inlineStr"/>
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>64519.04</v>
+        <v>62230.66</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1057539-8032-CM26</t>
+          <t>1057539-8024-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12818,7 +12818,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>SINERMED SPA</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>76.367.671-4</t>
         </is>
       </c>
       <c r="K199" t="inlineStr"/>
@@ -12858,13 +12858,13 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>12096.26</v>
+        <v>28095.39</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1057539-8040-CM26</t>
+          <t>1057539-7411-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12904,12 +12904,12 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K200" t="inlineStr"/>
@@ -12919,13 +12919,13 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>12096.26</v>
+        <v>64519.04</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>608-11651-CM26</t>
+          <t>1057539-7513-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12950,47 +12950,43 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>99.585.860-6</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>18524.55</v>
+        <v>70972.92999999999</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>608-11665-CM26</t>
+          <t>1057539-8032-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -13015,27 +13011,27 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K202" t="inlineStr"/>
@@ -13045,13 +13041,13 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>2870.44</v>
+        <v>12096.26</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1057539-7513-CM26</t>
+          <t>1057539-8040-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -13091,12 +13087,12 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>TECNOMEDICAL S A</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>99.585.860-6</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K203" t="inlineStr"/>
@@ -13106,13 +13102,13 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>70972.92999999999</v>
+        <v>12096.26</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>812030-974-CM26</t>
+          <t>608-11651-CM26</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -13127,7 +13123,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -13137,17 +13133,17 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -13171,13 +13167,13 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>4383.67</v>
+        <v>18524.55</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1549-4205-CM26</t>
+          <t>608-11665-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -13192,27 +13188,27 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -13232,7 +13228,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>72274.78</v>
+        <v>2870.44</v>
       </c>
     </row>
     <row r="206">
@@ -13303,7 +13299,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1057539-7515-CM26</t>
+          <t>812030-974-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13318,7 +13314,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -13328,43 +13324,47 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>TECNOMEDICAL S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>99.585.860-6</t>
-        </is>
-      </c>
-      <c r="K207" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>15634.34</v>
+        <v>4383.67</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>812030-952-CM26</t>
+          <t>1549-4205-CM26</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13379,7 +13379,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -13389,12 +13389,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13404,12 +13404,12 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K208" t="inlineStr"/>
@@ -13419,13 +13419,13 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>40018.36</v>
+        <v>72274.78</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1057539-8154-CM26</t>
+          <t>812030-952-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13445,32 +13445,32 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>SINERMED SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>76.367.671-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K209" t="inlineStr"/>
@@ -13480,13 +13480,13 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>5518</v>
+        <v>40018.36</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>812030-953-CM26</t>
+          <t>1057539-7515-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13506,32 +13506,32 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>99.585.860-6</t>
         </is>
       </c>
       <c r="K210" t="inlineStr"/>
@@ -13541,13 +13541,13 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>40858.64</v>
+        <v>15634.34</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>1057501-11049-CM26</t>
+          <t>1057539-8154-CM26</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13557,42 +13557,42 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>oct-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+          <t>SINERMED SPA</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>78.566.250-4</t>
+          <t>76.367.671-4</t>
         </is>
       </c>
       <c r="K211" t="inlineStr"/>
@@ -13602,13 +13602,13 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>3515.28</v>
+        <v>5518</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>1057539-8225-CM26</t>
+          <t>812030-953-CM26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13618,32 +13618,32 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>oct-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13663,13 +13663,13 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>9400.209999999999</v>
+        <v>40858.64</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1057539-8240-CM26</t>
+          <t>1057501-11049-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13684,37 +13684,37 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>SPINEX CORPORATION CHILE S.A</t>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>76.166.489-1</t>
+          <t>78.566.250-4</t>
         </is>
       </c>
       <c r="K213" t="inlineStr"/>
@@ -13724,13 +13724,13 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>43904.23</v>
+        <v>3515.28</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>1057539-8281-CM26</t>
+          <t>1057539-8225-CM26</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13745,7 +13745,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -13770,12 +13770,12 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>BIOIMPLANTES SA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>76.214.144-2</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K214" t="inlineStr"/>
@@ -13785,13 +13785,13 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>57072.05</v>
+        <v>9400.209999999999</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1057539-8284-CM26</t>
+          <t>1057539-8240-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13806,7 +13806,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -13831,32 +13831,28 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>AETICA SPA</t>
+          <t>SPINEX CORPORATION CHILE S.A</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>77.535.386-4</t>
-        </is>
-      </c>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.166.489-1</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr"/>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>63086.71</v>
+        <v>43904.23</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>1549-4364-CM26</t>
+          <t>1057539-8281-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13871,7 +13867,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -13881,27 +13877,27 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>BIOIMPLANTES SA</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.214.144-2</t>
         </is>
       </c>
       <c r="K216" t="inlineStr"/>
@@ -13911,13 +13907,13 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>65515.74</v>
+        <v>57072.05</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>1057539-8551-CM26</t>
+          <t>1057539-8284-CM26</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -13932,7 +13928,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -13957,28 +13953,32 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>AETICA SPA</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K217" t="inlineStr"/>
+          <t>77.535.386-4</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>3751.95</v>
+        <v>63086.71</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>812030-938-CM26</t>
+          <t>1549-4364-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -13993,7 +13993,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -14003,12 +14003,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -14033,13 +14033,13 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>21454.28</v>
+        <v>65515.74</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1057049-18804-CM26</t>
+          <t>1057539-8551-CM26</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -14054,37 +14054,37 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>HEMISFERIO SUR S.A.</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>96.533.330-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K219" t="inlineStr"/>
@@ -14094,13 +14094,13 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>6088.47</v>
+        <v>3751.95</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>1057417-16266-CM26</t>
+          <t>812030-938-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -14115,37 +14115,37 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K220" t="inlineStr"/>
@@ -14155,13 +14155,13 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>20205.85</v>
+        <v>21454.28</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1057417-16267-CM26</t>
+          <t>1057049-18804-CM26</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -14176,7 +14176,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -14186,27 +14186,27 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>HEMISFERIO SUR S.A.</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.533.330-4</t>
         </is>
       </c>
       <c r="K221" t="inlineStr"/>
@@ -14216,13 +14216,13 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>21599.84</v>
+        <v>6088.47</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>1057417-16268-CM26</t>
+          <t>1057417-16266-CM26</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -14277,13 +14277,13 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>39264.2</v>
+        <v>20205.85</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1057417-16269-CM26</t>
+          <t>1057417-16267-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14338,13 +14338,13 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>12602.06</v>
+        <v>21599.84</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2258-7501-CM26</t>
+          <t>1057417-16268-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14359,7 +14359,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -14369,17 +14369,17 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14399,13 +14399,13 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>8641.85</v>
+        <v>39264.2</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2258-7617-CM26</t>
+          <t>1057417-16269-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14420,7 +14420,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -14430,17 +14430,17 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -14460,13 +14460,13 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>3657.63</v>
+        <v>12602.06</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2258-7631-CM26</t>
+          <t>2258-7501-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14521,13 +14521,13 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>14857.81</v>
+        <v>8641.85</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2258-7911-CM26</t>
+          <t>2258-7617-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14547,7 +14547,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -14567,32 +14567,28 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
-        </is>
-      </c>
-      <c r="K227" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr"/>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>2544.74</v>
+        <v>3657.63</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1057417-16829-CM26</t>
+          <t>2258-7631-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -14612,52 +14608,48 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K228" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr"/>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>64527.95</v>
+        <v>14857.81</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1057539-8853-CM26</t>
+          <t>2258-7911-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -14672,7 +14664,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -14682,43 +14674,47 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>Sylex Biomédica Spa</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>76.015.781-3</t>
-        </is>
-      </c>
-      <c r="K229" t="inlineStr"/>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>3817.75</v>
+        <v>2544.74</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2258-8238-CM26</t>
+          <t>1057417-16829-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -14733,7 +14729,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -14743,43 +14739,47 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K230" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>20409.08</v>
+        <v>64527.95</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1057049-18978-CM26</t>
+          <t>1057539-8853-CM26</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -14794,7 +14794,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -14804,27 +14804,27 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>SINERMED SPA</t>
+          <t>Sylex Biomédica Spa</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>76.367.671-4</t>
+          <t>76.015.781-3</t>
         </is>
       </c>
       <c r="K231" t="inlineStr"/>
@@ -14834,13 +14834,13 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>11552.69</v>
+        <v>3817.75</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1057539-8282-CM26</t>
+          <t>2258-8238-CM26</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -14855,7 +14855,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -14865,27 +14865,27 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>BIOIMPLANTES SA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>76.214.144-2</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K232" t="inlineStr"/>
@@ -14895,71 +14895,193 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>57980.76</v>
+        <v>20409.08</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
+          <t>1057049-18978-CM26</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>61.608.604-9</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>SINERMED SPA</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>76.367.671-4</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr"/>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M233" s="2" t="n">
+        <v>11552.69</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>1057539-8282-CM26</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>BIOIMPLANTES SA</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>76.214.144-2</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr"/>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M234" s="2" t="n">
+        <v>57980.76</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
           <t>1057501-12037-CM26</t>
         </is>
       </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>2239-15-LR25</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
         <is>
           <t>oct-2026</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr">
+      <c r="D235" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="E233" t="inlineStr">
+      <c r="E235" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F233" t="inlineStr">
+      <c r="F235" t="inlineStr">
         <is>
           <t>61.608.502-6</t>
         </is>
       </c>
-      <c r="G233" t="inlineStr">
+      <c r="G235" t="inlineStr">
         <is>
           <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr">
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
         <is>
           <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
-      <c r="J233" t="inlineStr">
+      <c r="J235" t="inlineStr">
         <is>
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L233" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M233" s="2" t="n">
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M235" s="2" t="n">
         <v>2518.1</v>
       </c>
     </row>
